--- a/Sindhi Muslim/Office Computer/salarysheet Feb 2025.xlsx
+++ b/Sindhi Muslim/Office Computer/salarysheet Feb 2025.xlsx
@@ -1,18 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Office Computer\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46DBF18-7ED2-45EC-8906-C7163746E732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="525" windowWidth="22695" windowHeight="11445"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="February-2025" sheetId="1" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -286,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy"/>
@@ -886,7 +903,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="74">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1010,19 +1027,48 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1031,80 +1077,11 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC000"/>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1127,12 +1104,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Attandance"/>
@@ -1433,14 +1413,11 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}"/>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P101"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1460,58 +1437,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="68"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="55"/>
     </row>
     <row r="2" spans="1:15" ht="21">
-      <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
-      <c r="G2" s="70"/>
-      <c r="H2" s="70"/>
-      <c r="I2" s="70"/>
-      <c r="J2" s="70"/>
-      <c r="K2" s="70"/>
-      <c r="L2" s="70"/>
-      <c r="M2" s="70"/>
-      <c r="N2" s="71"/>
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="58"/>
     </row>
     <row r="4" spans="1:15" ht="26.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="54"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="61"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="1"/>
@@ -1530,82 +1507,82 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="51" t="s">
+      <c r="F6" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="51" t="s">
+      <c r="G6" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="72" t="s">
+      <c r="I6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="59"/>
-      <c r="K6" s="59"/>
-      <c r="L6" s="60"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="64"/>
       <c r="M6" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="61" t="s">
+      <c r="N6" s="66" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="56"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="66" t="s">
+      <c r="A7" s="71"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="66" t="s">
+      <c r="J7" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="K7" s="66" t="s">
+      <c r="K7" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="64" t="s">
+      <c r="L7" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="49"/>
-      <c r="N7" s="62"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="67"/>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="57"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="63"/>
+      <c r="A8" s="72"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="68"/>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
@@ -2036,7 +2013,7 @@
       <c r="N18" s="28">
         <v>28000</v>
       </c>
-      <c r="P18" s="73"/>
+      <c r="P18" s="48"/>
     </row>
     <row r="19" spans="1:16">
       <c r="A19" s="1"/>
@@ -2071,22 +2048,22 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:16" ht="26.25">
-      <c r="A21" s="52" t="s">
+      <c r="A21" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="54"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="60"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="61"/>
     </row>
     <row r="22" spans="1:16" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
@@ -2105,82 +2082,82 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="51" t="s">
+      <c r="E23" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="51" t="s">
+      <c r="G23" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="H23" s="51" t="s">
+      <c r="H23" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="I23" s="58" t="s">
+      <c r="I23" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="J23" s="59"/>
-      <c r="K23" s="59"/>
-      <c r="L23" s="60"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="64"/>
       <c r="M23" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="61" t="s">
+      <c r="N23" s="66" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A24" s="56"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="66" t="s">
+      <c r="A24" s="71"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="J24" s="66" t="s">
+      <c r="J24" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="K24" s="66" t="s">
+      <c r="K24" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="L24" s="64" t="s">
+      <c r="L24" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="M24" s="49"/>
-      <c r="N24" s="62"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="67"/>
     </row>
     <row r="25" spans="1:16" ht="15.75" customHeight="1">
-      <c r="A25" s="57"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="63"/>
+      <c r="A25" s="72"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="68"/>
     </row>
     <row r="26" spans="1:16" ht="15.75" customHeight="1">
       <c r="A26" s="29" t="s">
@@ -2558,6 +2535,24 @@
     <row r="101" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="N23:N25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="L24:L25"/>
+    <mergeCell ref="M23:M25"/>
+    <mergeCell ref="K24:K25"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="A21:N21"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="I24:I25"/>
@@ -2574,43 +2569,15 @@
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="A21:N21"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="N23:N25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="E23:E25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="L24:L25"/>
-    <mergeCell ref="M23:M25"/>
-    <mergeCell ref="K24:K25"/>
   </mergeCells>
-  <conditionalFormatting sqref="B9:M9 B10:C11 C12:C17 D27:E32 F26:F32 G32:J32 K27:M32 M10:M17 D10:L18 G27:I31">
-    <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$C9=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C26:C32">
-    <cfRule type="expression" dxfId="5" priority="2">
+  <conditionalFormatting sqref="B26:B31">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$C26=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26:B31 D26:E26 H26:M26 J27:J31">
-    <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$C26=#REF!</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G26">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$C26=#REF!</formula>
+  <conditionalFormatting sqref="B9:M9 B10:C11 M10:M17 D10:L18 C12:C17 C26:M32">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$C9=#REF!</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
